--- a/output/pdf_financials_xlsx/GEMC.xlsx
+++ b/output/pdf_financials_xlsx/GEMC.xlsx
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.365653</v>
+        <v>-0.365653</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.356653</v>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.365653</v>
+        <v>-0.365653</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.356653</v>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.365653</v>
+        <v>-0.365653</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.356653</v>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-2.437687</v>
+        <v>2.437687</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>2.377687</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.365653</v>
+        <v>-0.365653</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.356653</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.365653</v>
+        <v>-0.365653</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.356653</v>
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -4294,31 +4294,31 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.547401</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.686954</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.188112</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.166401</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.153351</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.958579</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.997148</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.840926</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.772123</v>
       </c>
     </row>
     <row r="93">
@@ -5379,31 +5379,31 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.247356</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.9916199999999999</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.24334</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.15211</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.212161</v>
+        <v>-0.034241</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.534559</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.109103</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.103522</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.041408</v>
       </c>
     </row>
     <row r="119">
@@ -7123,7 +7123,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -7700,7 +7704,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -10958,7 +10966,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -12877,7 +12889,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -32770,7 +32786,7 @@
         </is>
       </c>
       <c r="E383" s="5" t="n">
-        <v>0.365653</v>
+        <v>-0.365653</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GEMC.xlsx
+++ b/output/pdf_financials_xlsx/GEMC.xlsx
@@ -772,19 +772,19 @@
         <v>0.128907</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.191374</v>
+        <v>0.356653</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.04367</v>
+        <v>2.06143</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.5953270000000001</v>
+        <v>1.067115</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.246571</v>
+        <v>0.8739479999999999</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.136844</v>
+        <v>0.544947</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.247199</v>
@@ -812,7 +812,7 @@
         <v>-0.128907</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.191374</v>
+        <v>-0.356653</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>-2.06143</v>
@@ -821,7 +821,7 @@
         <v>-1.067115</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.246571</v>
+        <v>-0.8739479999999999</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>-0.544947</v>
@@ -1794,31 +1794,31 @@
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.492925</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.155708</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.324207</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000314</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.6315460000000001</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.382179</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.139979</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.035848</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.025587</v>
       </c>
     </row>
     <row r="35">
@@ -1878,31 +1878,31 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.492925</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.090881</v>
+        <v>0.246589</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.031363</v>
+        <v>0.35557</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.009652000000000001</v>
+        <v>0.009965999999999999</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.378244</v>
+        <v>1.00979</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.425095</v>
+        <v>0.807274</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1.113668</v>
+        <v>1.253647</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.8771870000000001</v>
+        <v>0.913035</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.896138</v>
+        <v>0.921725</v>
       </c>
     </row>
     <row r="37">
@@ -2382,31 +2382,31 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.638487</v>
+        <v>0.145562</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.172864</v>
+        <v>0.017156</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.468455</v>
+        <v>0.144248</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.000314</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.781546</v>
+        <v>0.15</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.459806</v>
+        <v>0.077627</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.139979</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.035848</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.05605</v>
+        <v>0.030463</v>
       </c>
     </row>
     <row r="49">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -30376,7 +30376,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -30385,19 +30385,19 @@
         </is>
       </c>
       <c r="F349" s="5" t="n">
-        <v>-0.356653</v>
+        <v>0.356653</v>
       </c>
       <c r="G349" s="5" t="n">
         <v>2.06143</v>
       </c>
       <c r="H349" s="5" t="n">
-        <v>-1.067115</v>
+        <v>1.067115</v>
       </c>
       <c r="I349" s="5" t="n">
-        <v>-0.8739479999999999</v>
+        <v>0.8739479999999999</v>
       </c>
       <c r="J349" s="5" t="n">
-        <v>-0.544947</v>
+        <v>0.544947</v>
       </c>
       <c r="K349" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -31997,7 +31997,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E372" s="5" t="n">

--- a/output/pdf_financials_xlsx/GEMC.xlsx
+++ b/output/pdf_financials_xlsx/GEMC.xlsx
@@ -3088,25 +3088,25 @@
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.075793</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.256779</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.313558</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.219222</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.323563</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.457326</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.385222</v>
       </c>
     </row>
     <row r="65">
@@ -3214,25 +3214,25 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.0255</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.022575</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.0375</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="68">
@@ -5268,10 +5268,10 @@
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.041329</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.015272</v>
       </c>
     </row>
     <row r="116">
@@ -12045,7 +12045,11 @@
           <t>Loss from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -12820,7 +12824,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -16112,7 +16120,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
